--- a/Extra/TestCase_CaroGame.xlsx
+++ b/Extra/TestCase_CaroGame.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\Network_Programming-UDM17_Group2\Extra\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
   <si>
     <t>No</t>
   </si>
@@ -178,6 +178,21 @@
   </si>
   <si>
     <t>TC_7 Proof</t>
+  </si>
+  <si>
+    <t>TC_8</t>
+  </si>
+  <si>
+    <t>Game – Đánh thắng 5 quân liên tiếp</t>
+  </si>
+  <si>
+    <t>Tạo đủ điều kiện thắng</t>
+  </si>
+  <si>
+    <t>Đánh đủ 5 quân X liên tiếp theo hàng ngang</t>
+  </si>
+  <si>
+    <t>Server phát hiện thắng, gửi packet WIN, hiện thông báo người thắng, khóa bàn cờ</t>
   </si>
 </sst>
 </file>
@@ -796,10 +811,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H9"/>
+  <dimension ref="B2:H10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="27.875" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="28.875" customWidth="1"/>
     <col min="5" max="5" width="55.25" customWidth="1"/>
     <col min="6" max="6" width="68" customWidth="1"/>
@@ -991,6 +1006,23 @@
         <v>48</v>
       </c>
     </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Extra/TestCase_CaroGame.xlsx
+++ b/Extra/TestCase_CaroGame.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="164">
   <si>
     <t>No</t>
   </si>
@@ -193,13 +193,353 @@
   </si>
   <si>
     <t>Server phát hiện thắng, gửi packet WIN, hiện thông báo người thắng, khóa bàn cờ</t>
+  </si>
+  <si>
+    <t>TC_9</t>
+  </si>
+  <si>
+    <t>Game – Hết lượt, không phải lượt mình</t>
+  </si>
+  <si>
+    <t>Click khi không phải lượt</t>
+  </si>
+  <si>
+    <t>Chưa tới lượt, click vào ô trống</t>
+  </si>
+  <si>
+    <t>MessageBox "Khong phai luot cua ban", board KHÔNG thay đổi</t>
+  </si>
+  <si>
+    <t>TC_10</t>
+  </si>
+  <si>
+    <t>Draw – Bàn cờ đầy không ai thắng</t>
+  </si>
+  <si>
+    <t>Hết ô trống, hòa</t>
+  </si>
+  <si>
+    <t>Đánh hết toàn bộ ô trên board không ai đủ 5 quân liên tiếp</t>
+  </si>
+  <si>
+    <t>Server gửi packet DRAW, hiện MessageBox "Hoa", khóa bàn cờ</t>
+  </si>
+  <si>
+    <t>TC_11</t>
+  </si>
+  <si>
+    <t>Network – Mất kết nối giữa trận</t>
+  </si>
+  <si>
+    <t>Client disconnect đột ngột</t>
+  </si>
+  <si>
+    <t>Ngắt kết nối mạng khi đang trong GameRoom</t>
+  </si>
+  <si>
+    <t>Server phát hiện disconnect, thông báo cho người chơi còn lại, kết thúc trận với trạng thái "Đối thủ rời trận"</t>
+  </si>
+  <si>
+    <t>TC_12</t>
+  </si>
+  <si>
+    <t>Network – Server không phản hồi (timeout)</t>
+  </si>
+  <si>
+    <t>Server treo/không gửi packet</t>
+  </si>
+  <si>
+    <t>Client gửi request nhưng không nhận phản hồi sau X giây</t>
+  </si>
+  <si>
+    <t>Hiện thông báo "Mat ket noi toi server", cho phép reconnect hoặc thoát</t>
+  </si>
+  <si>
+    <t>TC_13</t>
+  </si>
+  <si>
+    <t>History – Lưu lịch sử trận đấu</t>
+  </si>
+  <si>
+    <t>Kết thúc trận, lưu log</t>
+  </si>
+  <si>
+    <t>Trận đấu kết thúc (Win/Draw)</t>
+  </si>
+  <si>
+    <t>Lịch sử trận được lưu vào database/file, hiển thị đúng người thắng, thời gian, số nước đi</t>
+  </si>
+  <si>
+    <t>TC_14</t>
+  </si>
+  <si>
+    <t>History – Xem lại lịch sử trận cũ</t>
+  </si>
+  <si>
+    <t>Truy vấn lịch sử</t>
+  </si>
+  <si>
+    <t>Người dùng chọn xem History từ Lobby</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách các trận đã đấu, đúng thông tin từng trận</t>
+  </si>
+  <si>
+    <t>TC_15</t>
+  </si>
+  <si>
+    <t>Bot – Đánh với máy (AI)</t>
+  </si>
+  <si>
+    <t>Chế độ chơi với Bot</t>
+  </si>
+  <si>
+    <t>Chọn chế độ "Choi voi May", bắt đầu trận</t>
+  </si>
+  <si>
+    <t>Bot tự động đánh hợp lệ sau khi người chơi đánh xong, không vi phạm luật</t>
+  </si>
+  <si>
+    <t>TC_16</t>
+  </si>
+  <si>
+    <t>Bot – Bot chặn nước thắng của người chơi</t>
+  </si>
+  <si>
+    <t>Kiểm tra logic AI</t>
+  </si>
+  <si>
+    <t>Người chơi có 4 quân liên tiếp, sắp thắng</t>
+  </si>
+  <si>
+    <t>Bot ưu tiên đánh chặn vào ô có thể tạo 5 quân liên tiếp</t>
+  </si>
+  <si>
+    <t>TC_17</t>
+  </si>
+  <si>
+    <t>Login – Tên trùng người đang online</t>
+  </si>
+  <si>
+    <t>Trùng tên đăng nhập</t>
+  </si>
+  <si>
+    <t>Tên "Alice" đã tồn tại trên server</t>
+  </si>
+  <si>
+    <t>Server từ chối, hiện MessageBox "Ten da ton tai", KHÔNG mở LobbyForm</t>
+  </si>
+  <si>
+    <t>TC_18</t>
+  </si>
+  <si>
+    <t>Lobby – Mất kết nối khi đang trong Lobby</t>
+  </si>
+  <si>
+    <t>Disconnect tại Lobby</t>
+  </si>
+  <si>
+    <t>Ngắt mạng khi đang ở LobbyForm (chưa vào trận)</t>
+  </si>
+  <si>
+    <t>Hiện thông báo mất kết nối, quay về màn hình Login</t>
+  </si>
+  <si>
+    <t>TC_19</t>
+  </si>
+  <si>
+    <t>Bot – Chọn độ khó Easy/Medium/Hard</t>
+  </si>
+  <si>
+    <t>Cấu hình AI</t>
+  </si>
+  <si>
+    <t>Người chơi chọn độ khó trước khi vào trận với Bot</t>
+  </si>
+  <si>
+    <t>Bot điều chỉnh thuật toán đánh tương ứng (random/heuristic/minimax), lưu đúng cấu hình</t>
+  </si>
+  <si>
+    <t>TC_20</t>
+  </si>
+  <si>
+    <t>Bot – Bot đánh hợp lệ liên tục</t>
+  </si>
+  <si>
+    <t>Kiểm tra tính ổn định</t>
+  </si>
+  <si>
+    <t>Chơi 1 ván đầy đủ với Bot từ đầu đến khi kết thúc</t>
+  </si>
+  <si>
+    <t>Bot không bao giờ đánh vào ô đã có quân, không bị treo/lag giữa lượt</t>
+  </si>
+  <si>
+    <t>TC_21</t>
+  </si>
+  <si>
+    <t>Bot – Bot thắng khi đủ điều kiện</t>
+  </si>
+  <si>
+    <t>Logic thắng của AI</t>
+  </si>
+  <si>
+    <t>Bot tạo đủ 5 quân liên tiếp</t>
+  </si>
+  <si>
+    <t>Server công nhận Bot thắng, gửi packet WIN, hiện thông báo đúng</t>
+  </si>
+  <si>
+    <t>TC_22</t>
+  </si>
+  <si>
+    <t>Bot – Thời gian phản hồi của Bot</t>
+  </si>
+  <si>
+    <t>Hiệu năng AI</t>
+  </si>
+  <si>
+    <t>Bot phải tính nước đi trong giới hạn thời gian</t>
+  </si>
+  <si>
+    <t>Bot trả về nước đi trong &lt; X giây (ví dụ 2s), không làm treo UI</t>
+  </si>
+  <si>
+    <t>TC_23</t>
+  </si>
+  <si>
+    <t>Bot – Hủy trận đấu với Bot giữa chừng</t>
+  </si>
+  <si>
+    <t>Người chơi thoát sớm</t>
+  </si>
+  <si>
+    <t>Người chơi bấm "Thoát" khi đang đấu với Bot</t>
+  </si>
+  <si>
+    <t>Trận kết thúc ngay, không lưu vào lịch sử (hoặc lưu là "Bỏ trận" tùy thiết kế), quay về Lobby</t>
+  </si>
+  <si>
+    <t>TC_24</t>
+  </si>
+  <si>
+    <t>Chat – Gửi tin nhắn hợp lệ</t>
+  </si>
+  <si>
+    <t>Gửi chat trong trận</t>
+  </si>
+  <si>
+    <t>Người chơi nhập "gg wp" và nhấn Enter/Gửi</t>
+  </si>
+  <si>
+    <t>Tin nhắn được gửi qua server, hiển thị đúng trên khung chat của cả 2 người chơi, kèm tên người gửi</t>
+  </si>
+  <si>
+    <t>TC_25</t>
+  </si>
+  <si>
+    <t>Chat – Gửi tin nhắn rỗng</t>
+  </si>
+  <si>
+    <t>Bỏ trống nội dung</t>
+  </si>
+  <si>
+    <t>Nhấn nút Gửi khi ô chat trống</t>
+  </si>
+  <si>
+    <t>KHÔNG gửi packet CHAT, không có gì xuất hiện trên khung chat</t>
+  </si>
+  <si>
+    <t>TC_26</t>
+  </si>
+  <si>
+    <t>Chat – Tin nhắn quá dài</t>
+  </si>
+  <si>
+    <t>Giới hạn ký tự</t>
+  </si>
+  <si>
+    <t>Nhập chuỗi &gt; giới hạn cho phép (vd 200 ký tự)</t>
+  </si>
+  <si>
+    <t>Hệ thống cắt bớt hoặc hiện cảnh báo "Tin nhan qua dai", không gửi nguyên văn</t>
+  </si>
+  <si>
+    <t>TC_27</t>
+  </si>
+  <si>
+    <t>Chat – Nhận tin nhắn khi đang đánh cờ</t>
+  </si>
+  <si>
+    <t>Đồng thời với gameplay</t>
+  </si>
+  <si>
+    <t>Đối thủ gửi chat trong lúc mình đang suy nghĩ nước đi</t>
+  </si>
+  <si>
+    <t>Tin nhắn hiển thị ngay lập tức trên UI, KHÔNG ảnh hưởng đến trạng thái bàn cờ/lượt đi</t>
+  </si>
+  <si>
+    <t>TC_28</t>
+  </si>
+  <si>
+    <t>Chat – Spam tin nhắn liên tục</t>
+  </si>
+  <si>
+    <t>Kiểm tra chống spam (nếu có)</t>
+  </si>
+  <si>
+    <t>Gửi liên tục nhiều tin nhắn trong thời gian ngắn</t>
+  </si>
+  <si>
+    <t>Hệ thống giới hạn tần suất gửi (rate limit) hoặc cho phép tự do tùy thiết kế, không làm crash server</t>
+  </si>
+  <si>
+    <t>TC_29</t>
+  </si>
+  <si>
+    <t>Chat – Tin nhắn chứa ký tự đặc biệt/HTML injection</t>
+  </si>
+  <si>
+    <t>Kiểm tra bảo mật</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gửi nội dung như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>&lt;script&gt;alert(1)&lt;/script&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Nội dung được hiển thị dưới dạng text thuần (escape), KHÔNG thực thi mã, không gây lỗi UI</t>
+  </si>
+  <si>
+    <t>TC_30</t>
+  </si>
+  <si>
+    <t>Chat – Mất kết nối khi đang chat</t>
+  </si>
+  <si>
+    <t>Disconnect giữa chừng</t>
+  </si>
+  <si>
+    <t>Một bên ngắt mạng ngay sau khi gửi tin nhắn</t>
+  </si>
+  <si>
+    <t>Server xử lý disconnect đúng quy trình, tin nhắn đã gửi trước đó không bị mất ở phía người nhận (nếu đã đến server)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,6 +547,11 @@
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="3">
@@ -235,9 +580,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -811,18 +1159,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:H32"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="32.625" customWidth="1"/>
     <col min="4" max="4" width="28.875" customWidth="1"/>
     <col min="5" max="5" width="55.25" customWidth="1"/>
-    <col min="6" max="6" width="68" customWidth="1"/>
+    <col min="6" max="6" width="72.5" customWidth="1"/>
     <col min="7" max="7" width="15.625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -845,7 +1194,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:8" ht="49.5" customHeight="1">
       <c r="B3" t="s">
         <v>7</v>
       </c>
@@ -868,7 +1217,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:8" ht="36.75" customHeight="1">
       <c r="B4" t="s">
         <v>14</v>
       </c>
@@ -891,7 +1240,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" ht="39" customHeight="1">
       <c r="B5" t="s">
         <v>20</v>
       </c>
@@ -914,7 +1263,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:8" ht="40.5" customHeight="1">
       <c r="B6" t="s">
         <v>25</v>
       </c>
@@ -937,7 +1286,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:8" ht="34.5" customHeight="1">
       <c r="B7" t="s">
         <v>31</v>
       </c>
@@ -960,7 +1309,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:8" ht="41.25" customHeight="1">
       <c r="B8" t="s">
         <v>37</v>
       </c>
@@ -983,7 +1332,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:8" ht="37.5" customHeight="1">
       <c r="B9" t="s">
         <v>43</v>
       </c>
@@ -1006,7 +1355,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:8" ht="33.75" customHeight="1">
       <c r="B10" t="s">
         <v>49</v>
       </c>
@@ -1021,6 +1370,380 @@
       </c>
       <c r="F10" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="36.75" customHeight="1">
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="47.25" customHeight="1">
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="45" customHeight="1">
+      <c r="B13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="42" customHeight="1">
+      <c r="B14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="54.75" customHeight="1">
+      <c r="B15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="30" customHeight="1">
+      <c r="B16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="30" customHeight="1">
+      <c r="B17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="45.75" customHeight="1">
+      <c r="B18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="27" customHeight="1">
+      <c r="B19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="45" customHeight="1">
+      <c r="B20" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" ht="27.75" customHeight="1">
+      <c r="B21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" ht="45.75" customHeight="1">
+      <c r="B22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" t="s">
+        <v>112</v>
+      </c>
+      <c r="F22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" ht="36" customHeight="1">
+      <c r="B23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="27" customHeight="1">
+      <c r="B24" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" ht="30.75" customHeight="1">
+      <c r="B25" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="28.5">
+      <c r="B26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" ht="18.75" customHeight="1">
+      <c r="B27" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="28.5" customHeight="1">
+      <c r="B28" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" ht="28.5">
+      <c r="B29" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" ht="28.5">
+      <c r="B30" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" ht="28.5">
+      <c r="B31" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="28.5">
+      <c r="B32" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -1031,7 +1754,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1041,7 +1764,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1051,7 +1774,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1061,7 +1784,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1071,7 +1794,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1081,7 +1804,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1091,7 +1814,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Extra/TestCase_CaroGame.xlsx
+++ b/Extra/TestCase_CaroGame.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\Network_Programming-UDM17_Group2\Extra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf77919f0a43eb98/文档/Network_Programming-UDM17_Group2/Extra/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_1B820BA3B316C9A35CD36EC24D36F6C1B5AEF599" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C953323C-F8B8-475F-92FA-F12DFBD7683B}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -538,8 +539,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -552,6 +553,15 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -577,17 +587,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -620,7 +633,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -661,7 +680,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -702,7 +727,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -743,7 +774,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -784,7 +821,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -827,7 +870,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -870,7 +919,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1158,7 +1213,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1213,7 +1268,7 @@
       <c r="G3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1236,7 +1291,7 @@
       <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1259,7 +1314,7 @@
       <c r="G5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="3" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1282,7 +1337,7 @@
       <c r="G6" t="s">
         <v>12</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1305,7 +1360,7 @@
       <c r="G7" t="s">
         <v>12</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="3" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1328,7 +1383,7 @@
       <c r="G8" t="s">
         <v>12</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1351,7 +1406,7 @@
       <c r="G9" t="s">
         <v>12</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="3" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1747,12 +1802,21 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H3" location="'TC_1 Proof'!A1" display="TC_1 Proof" xr:uid="{256A3CB0-4B03-42B9-9ECD-66F3F951C647}"/>
+    <hyperlink ref="H4" location="'TC_2 Proof'!A1" display="TC_2 Proof" xr:uid="{2B643974-F390-4F89-8288-0ABCE7FD4A57}"/>
+    <hyperlink ref="H5" location="'TC_3 Proof'!A1" display="TC_3 Proof" xr:uid="{9D1BE21F-B384-4843-B460-9EE2C4EC7BEE}"/>
+    <hyperlink ref="H6" location="'TC_4 Proof'!A1" display="TC_4 Proof" xr:uid="{2BCB4D10-5BDB-4D38-9760-9DFBC6733520}"/>
+    <hyperlink ref="H7" location="'TC_5 Proof'!A1" display="TC_5 Proof" xr:uid="{9C448A85-2CB4-4D0C-A553-1A678A597FD7}"/>
+    <hyperlink ref="H8" location="'TC_6 Proof'!A1" display="TC_6 Proof" xr:uid="{1C220EE0-FB99-4213-ACFA-7EFFF8FA0701}"/>
+    <hyperlink ref="H9" location="'TC_7 Proof'!A1" display="TC_7 Proof" xr:uid="{FC4FC761-8E73-42C5-994B-60797F0F758F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
@@ -1762,7 +1826,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
@@ -1772,7 +1836,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
@@ -1782,7 +1846,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
@@ -1792,7 +1856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
@@ -1802,7 +1866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
@@ -1812,7 +1876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>

--- a/Extra/TestCase_CaroGame.xlsx
+++ b/Extra/TestCase_CaroGame.xlsx
@@ -1,25 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\Network_Programming-UDM17_Group2\Extra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Pictures\Network_Programming-UDM17_Group2\Extra\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2386D2D7-9937-43BC-A82F-0FAFC2D643AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="TC_1 Proof" sheetId="2" r:id="rId2"/>
-    <sheet name="TC_2 Proof" sheetId="3" r:id="rId3"/>
-    <sheet name="TC_3 Proof" sheetId="4" r:id="rId4"/>
-    <sheet name="TC_4 Proof" sheetId="5" r:id="rId5"/>
-    <sheet name="TC_5 Proof" sheetId="6" r:id="rId6"/>
-    <sheet name="TC_6 Proof" sheetId="7" r:id="rId7"/>
-    <sheet name="TC_7 Proof" sheetId="8" r:id="rId8"/>
+    <sheet name="TC_18 Proof" sheetId="14" r:id="rId2"/>
+    <sheet name="TC_17 Proof" sheetId="13" r:id="rId3"/>
+    <sheet name="TC_16 Proof" sheetId="12" r:id="rId4"/>
+    <sheet name="TC_15 Proof" sheetId="11" r:id="rId5"/>
+    <sheet name="TC_14 Proof" sheetId="10" r:id="rId6"/>
+    <sheet name="TC_13 Proof" sheetId="9" r:id="rId7"/>
+    <sheet name="TC_1 Proof" sheetId="2" r:id="rId8"/>
+    <sheet name="TC_2 Proof" sheetId="3" r:id="rId9"/>
+    <sheet name="TC_3 Proof" sheetId="4" r:id="rId10"/>
+    <sheet name="TC_4 Proof" sheetId="5" r:id="rId11"/>
+    <sheet name="TC_5 Proof" sheetId="6" r:id="rId12"/>
+    <sheet name="TC_6 Proof" sheetId="7" r:id="rId13"/>
+    <sheet name="TC_7 Proof" sheetId="8" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="171">
   <si>
     <t>No</t>
   </si>
@@ -534,16 +541,37 @@
   <si>
     <t>Server xử lý disconnect đúng quy trình, tin nhắn đã gửi trước đó không bị mất ở phía người nhận (nếu đã đến server)</t>
   </si>
+  <si>
+    <t>TC_13 Proof</t>
+  </si>
+  <si>
+    <t>TC_14 Proof</t>
+  </si>
+  <si>
+    <t>TC_15 Proof</t>
+  </si>
+  <si>
+    <t>TC_16 Proof</t>
+  </si>
+  <si>
+    <t>TC_17 Proof</t>
+  </si>
+  <si>
+    <t>TC_18 Proof</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -588,7 +616,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -613,15 +641,23 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>477337</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>29377</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
-        <xdr:cNvPicPr/>
+        <xdr:cNvPr id="3" name="Hình ảnh 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{783469DE-B3E5-E019-6078-CF6D9253754E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
@@ -632,7 +668,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="7124700" cy="4191000"/>
+          <a:ext cx="7792537" cy="5744377"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -644,89 +680,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>409574</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="7953374" cy="4772025"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>314324</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="9915524" cy="5772150"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -743,7 +697,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -767,7 +727,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -784,7 +744,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -810,7 +776,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -827,7 +793,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -853,7 +825,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -870,7 +842,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -885,6 +863,392 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="10571428" cy="7142857"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>534495</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>124587</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Hình ảnh 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4731257-A2F5-E0C0-4098-21CE5D7269E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7849695" cy="5458587"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>334868</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>124826</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Hình ảnh 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1284504C-390E-EFF4-4A7D-05221E2B66B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10698068" cy="7173326"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>353921</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>96247</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Hình ảnh 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADBE2B7C-70F3-C736-F1A8-90B674263D2E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10717121" cy="7144747"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>601180</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>172192</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Hình ảnh 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7220D5AD-0D92-889B-636A-187BD8B1F98E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7916380" cy="5315692"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>553548</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>162665</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Hình ảnh 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE1E81C6-E475-60A2-FA31-9E666D63DEBE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7868748" cy="5306165"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7124700" cy="4191000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>409574</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7953374" cy="4772025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>314324</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9915524" cy="5772150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1158,16 +1522,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H32"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="32.625" customWidth="1"/>
-    <col min="4" max="4" width="28.875" customWidth="1"/>
-    <col min="5" max="5" width="55.25" customWidth="1"/>
-    <col min="6" max="6" width="72.5" customWidth="1"/>
-    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" customWidth="1"/>
+    <col min="5" max="5" width="55.28515625" customWidth="1"/>
+    <col min="6" max="6" width="72.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1456,6 +1820,12 @@
       <c r="F15" s="2" t="s">
         <v>78</v>
       </c>
+      <c r="G15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="16" spans="2:8" ht="30" customHeight="1">
       <c r="B16" s="2" t="s">
@@ -1473,8 +1843,14 @@
       <c r="F16" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="17" spans="2:6" ht="30" customHeight="1">
+      <c r="G16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="30" customHeight="1">
       <c r="B17" s="2" t="s">
         <v>84</v>
       </c>
@@ -1490,8 +1866,14 @@
       <c r="F17" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" ht="45.75" customHeight="1">
+      <c r="G17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="45.75" customHeight="1">
       <c r="B18" s="2" t="s">
         <v>89</v>
       </c>
@@ -1507,8 +1889,14 @@
       <c r="F18" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" ht="27" customHeight="1">
+      <c r="G18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="27" customHeight="1">
       <c r="B19" s="2" t="s">
         <v>94</v>
       </c>
@@ -1524,8 +1912,14 @@
       <c r="F19" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" ht="45" customHeight="1">
+      <c r="G19" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="45" customHeight="1">
       <c r="B20" s="2" t="s">
         <v>99</v>
       </c>
@@ -1541,8 +1935,14 @@
       <c r="F20" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="21" spans="2:6" ht="27.75" customHeight="1">
+      <c r="G20" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="27.75" customHeight="1">
       <c r="B21" t="s">
         <v>104</v>
       </c>
@@ -1559,7 +1959,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="45.75" customHeight="1">
+    <row r="22" spans="2:8" ht="45.75" customHeight="1">
       <c r="B22" t="s">
         <v>109</v>
       </c>
@@ -1576,7 +1976,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="2:6" ht="36" customHeight="1">
+    <row r="23" spans="2:8" ht="36" customHeight="1">
       <c r="B23" t="s">
         <v>114</v>
       </c>
@@ -1593,7 +1993,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="2:6" ht="27" customHeight="1">
+    <row r="24" spans="2:8" ht="27" customHeight="1">
       <c r="B24" s="2" t="s">
         <v>119</v>
       </c>
@@ -1610,7 +2010,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="30.75" customHeight="1">
+    <row r="25" spans="2:8" ht="30.75" customHeight="1">
       <c r="B25" s="2" t="s">
         <v>124</v>
       </c>
@@ -1627,7 +2027,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="26" spans="2:6" ht="28.5">
+    <row r="26" spans="2:8" ht="30">
       <c r="B26" s="2" t="s">
         <v>129</v>
       </c>
@@ -1644,7 +2044,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="18.75" customHeight="1">
+    <row r="27" spans="2:8" ht="18.75" customHeight="1">
       <c r="B27" s="2" t="s">
         <v>134</v>
       </c>
@@ -1661,7 +2061,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="28.5" customHeight="1">
+    <row r="28" spans="2:8" ht="28.5" customHeight="1">
       <c r="B28" s="2" t="s">
         <v>139</v>
       </c>
@@ -1678,7 +2078,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="2:6" ht="28.5">
+    <row r="29" spans="2:8" ht="30">
       <c r="B29" s="2" t="s">
         <v>144</v>
       </c>
@@ -1695,7 +2095,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="28.5">
+    <row r="30" spans="2:8" ht="30">
       <c r="B30" s="2" t="s">
         <v>149</v>
       </c>
@@ -1712,7 +2112,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="2:6" ht="28.5">
+    <row r="31" spans="2:8" ht="30">
       <c r="B31" s="2" t="s">
         <v>154</v>
       </c>
@@ -1729,7 +2129,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="32" spans="2:6" ht="28.5">
+    <row r="32" spans="2:8" ht="30">
       <c r="B32" s="2" t="s">
         <v>159</v>
       </c>
@@ -1751,70 +2151,130 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76C502C3-D955-4D43-92AC-197D467819DA}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53934063-2735-4DD6-AE8A-2E07110B0DE2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA8E1100-81A7-4F1E-9E74-9C0D79583CC0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2BB8AA3-EE47-42D9-9FD1-F60BB28F77BC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F556CF5-6313-4FF1-92FA-DCCD167DC3F3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{687273F0-2DA0-4B20-9854-E83AD0907408}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Extra/TestCase_CaroGame.xlsx
+++ b/Extra/TestCase_CaroGame.xlsx
@@ -1,32 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Pictures\Network_Programming-UDM17_Group2\Extra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dowload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03540C88-1D40-4855-AFA8-C9BA4AF3B428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED8161A-5D11-4AEB-91D3-02AB6A37709C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="942" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="TC_18 Proof" sheetId="14" r:id="rId2"/>
-    <sheet name="TC_17 Proof" sheetId="13" r:id="rId3"/>
-    <sheet name="TC_16 Proof" sheetId="12" r:id="rId4"/>
-    <sheet name="TC_15 Proof" sheetId="11" r:id="rId5"/>
-    <sheet name="TC_14 Proof" sheetId="10" r:id="rId6"/>
-    <sheet name="TC_13 Proof" sheetId="9" r:id="rId7"/>
-    <sheet name="TC_1 Proof" sheetId="2" r:id="rId8"/>
-    <sheet name="TC_2 Proof" sheetId="3" r:id="rId9"/>
-    <sheet name="TC_3 Proof" sheetId="4" r:id="rId10"/>
-    <sheet name="TC_4 Proof" sheetId="5" r:id="rId11"/>
-    <sheet name="TC_5 Proof" sheetId="6" r:id="rId12"/>
-    <sheet name="TC_6 Proof" sheetId="7" r:id="rId13"/>
-    <sheet name="TC_7 Proof" sheetId="8" r:id="rId14"/>
+    <sheet name="TC_1 Proof" sheetId="2" r:id="rId2"/>
+    <sheet name="TC_2 Proof" sheetId="3" r:id="rId3"/>
+    <sheet name="TC_3 Proof" sheetId="4" r:id="rId4"/>
+    <sheet name="TC_4 Proof" sheetId="5" r:id="rId5"/>
+    <sheet name="TC_5 Proof" sheetId="6" r:id="rId6"/>
+    <sheet name="TC_6 Proof" sheetId="7" r:id="rId7"/>
+    <sheet name="TC_7 Proof" sheetId="8" r:id="rId8"/>
+    <sheet name="TC_8 Proof" sheetId="9" r:id="rId9"/>
+    <sheet name="TC_9 Proof" sheetId="10" r:id="rId10"/>
+    <sheet name="TC_10 Proof" sheetId="11" r:id="rId11"/>
+    <sheet name="TC_11 Proof" sheetId="12" r:id="rId12"/>
+    <sheet name="TC_12 Proof" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="170">
   <si>
     <t>No</t>
   </si>
@@ -519,6 +518,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
       </rPr>
       <t>&lt;script&gt;alert(1)&lt;/script&gt;</t>
     </r>
@@ -542,32 +542,29 @@
     <t>Server xử lý disconnect đúng quy trình, tin nhắn đã gửi trước đó không bị mất ở phía người nhận (nếu đã đến server)</t>
   </si>
   <si>
-    <t>TC_13 Proof</t>
-  </si>
-  <si>
-    <t>TC_14 Proof</t>
-  </si>
-  <si>
-    <t>TC_15 Proof</t>
-  </si>
-  <si>
-    <t>TC_16 Proof</t>
-  </si>
-  <si>
-    <t>TC_17 Proof</t>
-  </si>
-  <si>
-    <t>TC_18 Proof</t>
+    <t>TC_8 Proof</t>
+  </si>
+  <si>
+    <t>TC_9 Proof</t>
+  </si>
+  <si>
+    <t>TC_10 Proof</t>
+  </si>
+  <si>
+    <t>TC_11 Proof</t>
   </si>
   <si>
     <t>Fail</t>
+  </si>
+  <si>
+    <t>TC_12 Proof</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,6 +577,25 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -605,18 +621,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -641,17 +663,64 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>477337</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>29377</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Hình ảnh 2">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{783469DE-B3E5-E019-6078-CF6D9253754E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7124700" cy="4191000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>206656</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>145395</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{574DBFD1-5E52-9412-0786-7870F1B9C472}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -668,7 +737,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="7792537" cy="5744377"/>
+          <a:ext cx="10569856" cy="7094835"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -680,7 +749,199 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>244759</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>175877</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97EEFC22-E16D-B961-0CAA-C29B98156DB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10607959" cy="7125317"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>404529</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>38563</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE1EECD5-0A3C-93AB-439C-C380BE798BB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7719729" cy="5342083"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>409574</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7953374" cy="4772025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>314324</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9915524" cy="5772150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -727,7 +988,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -776,7 +1037,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -825,7 +1086,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -874,7 +1135,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -884,17 +1145,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>534495</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>124587</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>229518</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>114912</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Hình ảnh 1">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4731257-A2F5-E0C0-4098-21CE5D7269E5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D01E216-26B0-E651-7597-4D16B8AF692D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -911,7 +1172,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="7849695" cy="5458587"/>
+          <a:ext cx="10592718" cy="7064352"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -923,7 +1184,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -934,16 +1195,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>334868</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>124826</xdr:rowOff>
+      <xdr:colOff>206656</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>114912</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Hình ảnh 1">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1284504C-390E-EFF4-4A7D-05221E2B66B2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6800416C-6E45-ADBC-86D9-E7D86ADFA3E3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -960,295 +1221,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="10698068" cy="7173326"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>353921</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>96247</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Hình ảnh 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADBE2B7C-70F3-C736-F1A8-90B674263D2E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="10717121" cy="7144747"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>601180</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>172192</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Hình ảnh 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7220D5AD-0D92-889B-636A-187BD8B1F98E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="7916380" cy="5315692"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>553548</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>162665</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Hình ảnh 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE1E81C6-E475-60A2-FA31-9E666D63DEBE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="7868748" cy="5306165"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="7124700" cy="4191000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>409574</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="7953374" cy="4772025"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>314324</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="9915524" cy="5772150"/>
+          <a:ext cx="10569856" cy="7064352"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1524,18 +1497,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" customWidth="1"/>
-    <col min="5" max="5" width="55.28515625" customWidth="1"/>
-    <col min="6" max="6" width="72.42578125" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" customWidth="1"/>
+    <col min="4" max="4" width="28.88671875" customWidth="1"/>
+    <col min="5" max="5" width="55.21875" customWidth="1"/>
+    <col min="6" max="6" width="72.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1558,7 +1531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="49.5" customHeight="1">
+    <row r="3" spans="2:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>7</v>
       </c>
@@ -1577,11 +1550,11 @@
       <c r="G3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="36.75" customHeight="1">
+    <row r="4" spans="2:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>14</v>
       </c>
@@ -1600,11 +1573,11 @@
       <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="39" customHeight="1">
+    <row r="5" spans="2:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>20</v>
       </c>
@@ -1623,11 +1596,11 @@
       <c r="G5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="40.5" customHeight="1">
+    <row r="6" spans="2:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>25</v>
       </c>
@@ -1646,11 +1619,11 @@
       <c r="G6" t="s">
         <v>12</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="34.5" customHeight="1">
+    <row r="7" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>31</v>
       </c>
@@ -1669,11 +1642,11 @@
       <c r="G7" t="s">
         <v>12</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="41.25" customHeight="1">
+    <row r="8" spans="2:8" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>37</v>
       </c>
@@ -1692,11 +1665,11 @@
       <c r="G8" t="s">
         <v>12</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="37.5" customHeight="1">
+    <row r="9" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>43</v>
       </c>
@@ -1715,11 +1688,11 @@
       <c r="G9" t="s">
         <v>12</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="33.75" customHeight="1">
+    <row r="10" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>49</v>
       </c>
@@ -1735,8 +1708,14 @@
       <c r="F10" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="11" spans="2:8" ht="36.75" customHeight="1">
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>54</v>
       </c>
@@ -1752,8 +1731,14 @@
       <c r="F11" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="12" spans="2:8" ht="47.25" customHeight="1">
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>59</v>
       </c>
@@ -1769,8 +1754,14 @@
       <c r="F12" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="13" spans="2:8" ht="45" customHeight="1">
+      <c r="G12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>64</v>
       </c>
@@ -1786,8 +1777,14 @@
       <c r="F13" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="14" spans="2:8" ht="42" customHeight="1">
+      <c r="G13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>69</v>
       </c>
@@ -1803,8 +1800,14 @@
       <c r="F14" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" ht="54.75" customHeight="1">
+      <c r="G14" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>74</v>
       </c>
@@ -1820,14 +1823,8 @@
       <c r="F15" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" ht="30" customHeight="1">
+    </row>
+    <row r="16" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>79</v>
       </c>
@@ -1843,14 +1840,8 @@
       <c r="F16" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" ht="30" customHeight="1">
+    </row>
+    <row r="17" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>84</v>
       </c>
@@ -1866,14 +1857,8 @@
       <c r="F17" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="45.75" customHeight="1">
+    </row>
+    <row r="18" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>89</v>
       </c>
@@ -1889,14 +1874,8 @@
       <c r="F18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="27" customHeight="1">
+    </row>
+    <row r="19" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>94</v>
       </c>
@@ -1912,14 +1891,8 @@
       <c r="F19" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="45" customHeight="1">
+    </row>
+    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>99</v>
       </c>
@@ -1935,14 +1908,8 @@
       <c r="F20" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" ht="27.75" customHeight="1">
+    </row>
+    <row r="21" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>104</v>
       </c>
@@ -1959,7 +1926,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="45.75" customHeight="1">
+    <row r="22" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>109</v>
       </c>
@@ -1976,7 +1943,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="36" customHeight="1">
+    <row r="23" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>114</v>
       </c>
@@ -1993,7 +1960,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="27" customHeight="1">
+    <row r="24" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>119</v>
       </c>
@@ -2010,7 +1977,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="30.75" customHeight="1">
+    <row r="25" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>124</v>
       </c>
@@ -2027,7 +1994,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="30">
+    <row r="26" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>129</v>
       </c>
@@ -2044,7 +2011,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="18.75" customHeight="1">
+    <row r="27" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
         <v>134</v>
       </c>
@@ -2061,7 +2028,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="28.5" customHeight="1">
+    <row r="28" spans="2:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
         <v>139</v>
       </c>
@@ -2078,7 +2045,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="30">
+    <row r="29" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
         <v>144</v>
       </c>
@@ -2095,7 +2062,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="30">
+    <row r="30" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
         <v>149</v>
       </c>
@@ -2112,7 +2079,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="30">
+    <row r="31" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
         <v>154</v>
       </c>
@@ -2129,7 +2096,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="30">
+    <row r="32" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
         <v>159</v>
       </c>
@@ -2147,14 +2114,28 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H3" location="'TC_1 Proof'!A1" display="TC_1 Proof" xr:uid="{256A3CB0-4B03-42B9-9ECD-66F3F951C647}"/>
+    <hyperlink ref="H4" location="'TC_2 Proof'!A1" display="TC_2 Proof" xr:uid="{2B643974-F390-4F89-8288-0ABCE7FD4A57}"/>
+    <hyperlink ref="H5" location="'TC_3 Proof'!A1" display="TC_3 Proof" xr:uid="{9D1BE21F-B384-4843-B460-9EE2C4EC7BEE}"/>
+    <hyperlink ref="H6" location="'TC_4 Proof'!A1" display="TC_4 Proof" xr:uid="{2BCB4D10-5BDB-4D38-9760-9DFBC6733520}"/>
+    <hyperlink ref="H7" location="'TC_5 Proof'!A1" display="TC_5 Proof" xr:uid="{9C448A85-2CB4-4D0C-A553-1A678A597FD7}"/>
+    <hyperlink ref="H8" location="'TC_6 Proof'!A1" display="TC_6 Proof" xr:uid="{1C220EE0-FB99-4213-ACFA-7EFFF8FA0701}"/>
+    <hyperlink ref="H9" location="'TC_7 Proof'!A1" display="TC_7 Proof" xr:uid="{FC4FC761-8E73-42C5-994B-60797F0F758F}"/>
+    <hyperlink ref="H10" location="'TC_8 Proof'!A1" display="'TC_8 Proof'!A1" xr:uid="{A252847F-D1EF-41C2-8E85-D8ACBA0F08D0}"/>
+    <hyperlink ref="H11" location="'TC_9 Proof'!A1" display="'TC_9 Proof'!A1" xr:uid="{2E26452B-B9F7-4DFA-BF0E-9D972C42ADE0}"/>
+    <hyperlink ref="H12" location="'TC_10 Proof'!A1" display="TC_10 Proof" xr:uid="{E62B306C-09DE-44AF-98DE-7AE04F83E239}"/>
+    <hyperlink ref="H13" location="'TC_11 Proof'!A1" display="TC_11 Proof" xr:uid="{7CD9BD84-B509-41F3-A586-D84029831D0C}"/>
+    <hyperlink ref="H14" location="'TC_12 Proof'!A1" display="TC_12 Proof" xr:uid="{A1631DAA-D527-4EC0-9FB4-96FF24699C9C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8222F65D-9425-4F3F-8617-B3720678BA88}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2162,9 +2143,9 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14661779-2974-4C8F-A649-7A3252EF9A63}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2172,9 +2153,9 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD94721-2605-46E8-9976-CD8971097348}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2182,99 +2163,89 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{637A21EA-F0D3-4556-9E93-B67F4B7E162B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76C502C3-D955-4D43-92AC-197D467819DA}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53934063-2735-4DD6-AE8A-2E07110B0DE2}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA8E1100-81A7-4F1E-9E74-9C0D79583CC0}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2BB8AA3-EE47-42D9-9FD1-F60BB28F77BC}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F556CF5-6313-4FF1-92FA-DCCD167DC3F3}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{687273F0-2DA0-4B20-9854-E83AD0907408}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807BB318-320C-472B-B894-0C24E2BAB008}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Extra/TestCase_CaroGame.xlsx
+++ b/Extra/TestCase_CaroGame.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dowload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uteduvn-my.sharepoint.com/personal/nguyettta8540_ut_edu_vn/Documents/Documents/Network_Programming-UDM17_Group 2/Extra/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED8161A-5D11-4AEB-91D3-02AB6A37709C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{4ED8161A-5D11-4AEB-91D3-02AB6A37709C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03701A0A-81EB-4008-A30B-6BFCA43FF133}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="942" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="942" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,11 @@
     <sheet name="TC_10 Proof" sheetId="11" r:id="rId11"/>
     <sheet name="TC_11 Proof" sheetId="12" r:id="rId12"/>
     <sheet name="TC_12 Proof" sheetId="13" r:id="rId13"/>
+    <sheet name="TC_19 Proof" sheetId="14" r:id="rId14"/>
+    <sheet name="TC_20 Proof" sheetId="15" r:id="rId15"/>
+    <sheet name="TC_21 Proof" sheetId="16" r:id="rId16"/>
+    <sheet name="TC_22 Proof" sheetId="17" r:id="rId17"/>
+    <sheet name="TC_23 Proof" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="175">
   <si>
     <t>No</t>
   </si>
@@ -559,16 +564,31 @@
   <si>
     <t>TC_12 Proof</t>
   </si>
+  <si>
+    <t>TC_19 Proof</t>
+  </si>
+  <si>
+    <t>TC_ 20 Proof</t>
+  </si>
+  <si>
+    <t>TC_21 Proof</t>
+  </si>
+  <si>
+    <t>TC_22 Proof</t>
+  </si>
+  <si>
+    <t>TC_23 Proof</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -583,7 +603,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -592,7 +612,24 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -625,7 +662,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -635,6 +672,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -847,6 +889,251 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>655181</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>171221</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5DBE37F-4CDA-4961-AC33-66D3F7A4C59E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9900781" cy="5327421"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>292726</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>165428</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{510CC820-BECF-43BB-A67B-514E5B3C5594}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12179926" cy="6388428"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>254624</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>25730</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7B33F73-05D9-4DBF-8E41-E466FC729513}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12141824" cy="6426530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>45063</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>108275</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFF408DA-CB91-4209-9E4D-61B229418AC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="11932263" cy="6331275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>292726</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>63823</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED0AB014-87F8-43BB-90DC-66D0F8B4FFD0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12179926" cy="6286823"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -1231,6 +1518,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1496,19 +1787,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:I32"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="4" max="4" width="28.88671875" customWidth="1"/>
-    <col min="5" max="5" width="55.21875" customWidth="1"/>
-    <col min="6" max="6" width="72.44140625" customWidth="1"/>
+    <col min="4" max="4" width="28.9140625" customWidth="1"/>
+    <col min="5" max="5" width="55.25" customWidth="1"/>
+    <col min="6" max="6" width="72.4140625" customWidth="1"/>
     <col min="7" max="7" width="15.6640625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1531,7 +1822,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" ht="49.5" customHeight="1">
       <c r="B3" t="s">
         <v>7</v>
       </c>
@@ -1554,7 +1845,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" ht="36.75" customHeight="1">
       <c r="B4" t="s">
         <v>14</v>
       </c>
@@ -1577,7 +1868,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="39" customHeight="1">
       <c r="B5" t="s">
         <v>20</v>
       </c>
@@ -1600,7 +1891,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="40.5" customHeight="1">
       <c r="B6" t="s">
         <v>25</v>
       </c>
@@ -1623,7 +1914,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="34.5" customHeight="1">
       <c r="B7" t="s">
         <v>31</v>
       </c>
@@ -1646,7 +1937,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="41.25" customHeight="1">
       <c r="B8" t="s">
         <v>37</v>
       </c>
@@ -1669,7 +1960,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" ht="37.5" customHeight="1">
       <c r="B9" t="s">
         <v>43</v>
       </c>
@@ -1692,7 +1983,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" ht="33.75" customHeight="1">
       <c r="B10" t="s">
         <v>49</v>
       </c>
@@ -1715,7 +2006,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" ht="36.75" customHeight="1">
       <c r="B11" t="s">
         <v>54</v>
       </c>
@@ -1738,7 +2029,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" ht="47.25" customHeight="1">
       <c r="B12" t="s">
         <v>59</v>
       </c>
@@ -1761,7 +2052,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" ht="45" customHeight="1">
       <c r="B13" s="2" t="s">
         <v>64</v>
       </c>
@@ -1784,7 +2075,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" ht="42" customHeight="1">
       <c r="B14" s="2" t="s">
         <v>69</v>
       </c>
@@ -1807,7 +2098,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" ht="54.75" customHeight="1">
       <c r="B15" s="2" t="s">
         <v>74</v>
       </c>
@@ -1824,7 +2115,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" ht="30" customHeight="1">
       <c r="B16" s="2" t="s">
         <v>79</v>
       </c>
@@ -1841,7 +2132,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="30" customHeight="1">
       <c r="B17" s="2" t="s">
         <v>84</v>
       </c>
@@ -1858,7 +2149,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="45.75" customHeight="1">
       <c r="B18" s="2" t="s">
         <v>89</v>
       </c>
@@ -1874,8 +2165,10 @@
       <c r="F18" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="2:9" ht="27" customHeight="1">
       <c r="B19" s="2" t="s">
         <v>94</v>
       </c>
@@ -1891,8 +2184,10 @@
       <c r="F19" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" spans="2:9" ht="45" customHeight="1">
       <c r="B20" s="2" t="s">
         <v>99</v>
       </c>
@@ -1908,8 +2203,10 @@
       <c r="F20" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="21" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" spans="2:9" ht="27.75" customHeight="1">
       <c r="B21" t="s">
         <v>104</v>
       </c>
@@ -1925,8 +2222,15 @@
       <c r="F21" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="22" spans="2:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" spans="2:9" ht="45.75" customHeight="1">
       <c r="B22" t="s">
         <v>109</v>
       </c>
@@ -1942,8 +2246,15 @@
       <c r="F22" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="23" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" spans="2:9" ht="36" customHeight="1">
       <c r="B23" t="s">
         <v>114</v>
       </c>
@@ -1959,8 +2270,14 @@
       <c r="F23" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="24" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G23" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="27" customHeight="1">
       <c r="B24" s="2" t="s">
         <v>119</v>
       </c>
@@ -1976,8 +2293,14 @@
       <c r="F24" s="2" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="25" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="30.75" customHeight="1">
       <c r="B25" s="2" t="s">
         <v>124</v>
       </c>
@@ -1993,8 +2316,14 @@
       <c r="F25" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="26" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G25" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="28">
       <c r="B26" s="2" t="s">
         <v>129</v>
       </c>
@@ -2011,7 +2340,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" ht="18.75" customHeight="1">
       <c r="B27" s="2" t="s">
         <v>134</v>
       </c>
@@ -2028,7 +2357,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" ht="28.5" customHeight="1">
       <c r="B28" s="2" t="s">
         <v>139</v>
       </c>
@@ -2045,7 +2374,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9">
       <c r="B29" s="2" t="s">
         <v>144</v>
       </c>
@@ -2062,7 +2391,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" ht="28">
       <c r="B30" s="2" t="s">
         <v>149</v>
       </c>
@@ -2079,7 +2408,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:9" ht="28">
       <c r="B31" s="2" t="s">
         <v>154</v>
       </c>
@@ -2096,7 +2425,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="32" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:9" ht="28">
       <c r="B32" s="2" t="s">
         <v>159</v>
       </c>
@@ -2127,6 +2456,11 @@
     <hyperlink ref="H12" location="'TC_10 Proof'!A1" display="TC_10 Proof" xr:uid="{E62B306C-09DE-44AF-98DE-7AE04F83E239}"/>
     <hyperlink ref="H13" location="'TC_11 Proof'!A1" display="TC_11 Proof" xr:uid="{7CD9BD84-B509-41F3-A586-D84029831D0C}"/>
     <hyperlink ref="H14" location="'TC_12 Proof'!A1" display="TC_12 Proof" xr:uid="{A1631DAA-D527-4EC0-9FB4-96FF24699C9C}"/>
+    <hyperlink ref="H21" location="'TC_19 Proof'!A1" display="TC_19 Proof" xr:uid="{88801C26-4BCE-4166-9ED5-E032085C2F1C}"/>
+    <hyperlink ref="H22" location="'TC_20 Proof'!A1" display="TC_ 20 Proof" xr:uid="{8A8108D8-C593-4062-93F8-9AAE75D6870F}"/>
+    <hyperlink ref="H23" location="'TC_21 Proof'!A1" display="TC_21 Proof" xr:uid="{CAAD97C3-3420-4F49-BCCA-D75D8B80AB8F}"/>
+    <hyperlink ref="H24" location="'TC_22 Proof'!A1" display="TC_22 Proof" xr:uid="{C0E0F771-D2FB-46E8-B46B-518894807AAE}"/>
+    <hyperlink ref="H25" location="'TC_23 Proof'!A1" display="TC_23 Proof" xr:uid="{24451747-D40D-4C32-8024-28412E7008EC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2135,7 +2469,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8222F65D-9425-4F3F-8617-B3720678BA88}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2145,7 +2479,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14661779-2974-4C8F-A649-7A3252EF9A63}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2155,7 +2489,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD94721-2605-46E8-9976-CD8971097348}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2165,87 +2499,137 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{637A21EA-F0D3-4556-9E93-B67F4B7E162B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B60C7F1-5496-4F79-A385-AA9E21CF3764}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5C26EE5-A387-4DEB-AF12-3C60E522327E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A90DD207-1495-4605-80D8-A455910D4B21}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FF9CC2B-650A-4A14-8506-33F382FBF334}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56E205E1-D54B-4272-8EC7-61B3ED6CECA9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807BB318-320C-472B-B894-0C24E2BAB008}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Extra/TestCase_CaroGame.xlsx
+++ b/Extra/TestCase_CaroGame.xlsx
@@ -5,32 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uteduvn-my.sharepoint.com/personal/nguyettta8540_ut_edu_vn/Documents/Documents/Network_Programming-UDM17_Group 2/Extra/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Pictures\Network_Programming-UDM17_Group2\Extra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{4ED8161A-5D11-4AEB-91D3-02AB6A37709C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03701A0A-81EB-4008-A30B-6BFCA43FF133}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFCD827-E087-40F4-A5EE-1A108279E75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="942" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="942" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="TC_1 Proof" sheetId="2" r:id="rId2"/>
-    <sheet name="TC_2 Proof" sheetId="3" r:id="rId3"/>
-    <sheet name="TC_3 Proof" sheetId="4" r:id="rId4"/>
-    <sheet name="TC_4 Proof" sheetId="5" r:id="rId5"/>
-    <sheet name="TC_5 Proof" sheetId="6" r:id="rId6"/>
-    <sheet name="TC_6 Proof" sheetId="7" r:id="rId7"/>
-    <sheet name="TC_7 Proof" sheetId="8" r:id="rId8"/>
-    <sheet name="TC_8 Proof" sheetId="9" r:id="rId9"/>
-    <sheet name="TC_9 Proof" sheetId="10" r:id="rId10"/>
-    <sheet name="TC_10 Proof" sheetId="11" r:id="rId11"/>
-    <sheet name="TC_11 Proof" sheetId="12" r:id="rId12"/>
-    <sheet name="TC_12 Proof" sheetId="13" r:id="rId13"/>
-    <sheet name="TC_19 Proof" sheetId="14" r:id="rId14"/>
-    <sheet name="TC_20 Proof" sheetId="15" r:id="rId15"/>
-    <sheet name="TC_21 Proof" sheetId="16" r:id="rId16"/>
-    <sheet name="TC_22 Proof" sheetId="17" r:id="rId17"/>
-    <sheet name="TC_23 Proof" sheetId="18" r:id="rId18"/>
+    <sheet name="TC_14 Proof" sheetId="20" r:id="rId2"/>
+    <sheet name="TC_15 Proof" sheetId="21" r:id="rId3"/>
+    <sheet name="TC_16 Proof" sheetId="22" r:id="rId4"/>
+    <sheet name="TC_17 Proof" sheetId="23" r:id="rId5"/>
+    <sheet name="TC_18 Proof" sheetId="24" r:id="rId6"/>
+    <sheet name="TC_13 Proof" sheetId="19" r:id="rId7"/>
+    <sheet name="TC_1 Proof" sheetId="2" r:id="rId8"/>
+    <sheet name="TC_2 Proof" sheetId="3" r:id="rId9"/>
+    <sheet name="TC_3 Proof" sheetId="4" r:id="rId10"/>
+    <sheet name="TC_4 Proof" sheetId="5" r:id="rId11"/>
+    <sheet name="TC_5 Proof" sheetId="6" r:id="rId12"/>
+    <sheet name="TC_6 Proof" sheetId="7" r:id="rId13"/>
+    <sheet name="TC_7 Proof" sheetId="8" r:id="rId14"/>
+    <sheet name="TC_8 Proof" sheetId="9" r:id="rId15"/>
+    <sheet name="TC_9 Proof" sheetId="10" r:id="rId16"/>
+    <sheet name="TC_10 Proof" sheetId="11" r:id="rId17"/>
+    <sheet name="TC_11 Proof" sheetId="12" r:id="rId18"/>
+    <sheet name="TC_12 Proof" sheetId="13" r:id="rId19"/>
+    <sheet name="TC_19 Proof" sheetId="14" r:id="rId20"/>
+    <sheet name="TC_20 Proof" sheetId="15" r:id="rId21"/>
+    <sheet name="TC_21 Proof" sheetId="16" r:id="rId22"/>
+    <sheet name="TC_22 Proof" sheetId="17" r:id="rId23"/>
+    <sheet name="TC_23 Proof" sheetId="18" r:id="rId24"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -42,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="181">
   <si>
     <t>No</t>
   </si>
@@ -579,6 +585,24 @@
   <si>
     <t>TC_23 Proof</t>
   </si>
+  <si>
+    <t>TC_13 Proof</t>
+  </si>
+  <si>
+    <t>TC_14 Proof</t>
+  </si>
+  <si>
+    <t>TC_15 Proof</t>
+  </si>
+  <si>
+    <t>TC_16 Proof</t>
+  </si>
+  <si>
+    <t>TC_17 Proof</t>
+  </si>
+  <si>
+    <t>TC_18 Proof</t>
+  </si>
 </sst>
 </file>
 
@@ -588,7 +612,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -603,7 +627,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -612,7 +636,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -620,7 +644,7 @@
     <font>
       <sz val="11"/>
       <color theme="8"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -629,7 +653,7 @@
       <u/>
       <sz val="11"/>
       <color theme="8"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -662,7 +686,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -677,10 +701,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Siêu kết nối" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -705,17 +732,66 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>601180</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>172192</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Hình ảnh 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{637C7C3C-118E-48F0-94AB-CCA114FE77F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7916380" cy="5315692"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>333374</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -730,7 +806,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="7124700" cy="4191000"/>
+          <a:ext cx="7191374" cy="4714874"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -742,7 +818,252 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>256200</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>27893</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7800000" cy="5457143"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>180009</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>8845</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7723809" cy="5438095"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>284428</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>84832</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10571428" cy="7142857"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>229518</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>114912</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D01E216-26B0-E651-7597-4D16B8AF692D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10592718" cy="7064352"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>206656</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>114912</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6800416C-6E45-ADBC-86D9-E7D86ADFA3E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10569856" cy="7064352"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -791,7 +1112,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -840,7 +1161,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -889,7 +1210,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -938,7 +1259,56 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>353921</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>96247</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Hình ảnh 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F7C171E-6F88-4D80-A5C2-203F28681970}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10717121" cy="7144747"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -987,7 +1357,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1036,7 +1406,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1085,7 +1455,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1134,7 +1504,250 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>334868</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>124826</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Hình ảnh 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA8067A3-0873-4E4D-A161-33E2E7FCE213}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10698068" cy="7173326"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>534495</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>124587</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Hình ảnh 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E34D74DF-7D89-4E18-A928-2A88CA8282F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7849695" cy="5458587"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>477337</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>29377</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Hình ảnh 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C30B1B2-7E04-4771-802D-518C115B68F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7792537" cy="5744377"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>586205</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>162665</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Hình ảnh 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56A70FDA-0155-4C2B-B8D8-119C781907BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7901405" cy="5306165"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7124700" cy="4191000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1181,7 +1794,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1226,302 +1839,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>333374</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="7191374" cy="4714874"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>256200</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>27893</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="7800000" cy="5457143"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>180009</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>8845</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="7723809" cy="5438095"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>284428</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>84832</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="10571428" cy="7142857"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>229518</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>114912</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D01E216-26B0-E651-7597-4D16B8AF692D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="10592718" cy="7064352"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>206656</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>114912</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6800416C-6E45-ADBC-86D9-E7D86ADFA3E3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="10569856" cy="7064352"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1788,14 +2105,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:I32"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="4" max="4" width="28.9140625" customWidth="1"/>
-    <col min="5" max="5" width="55.25" customWidth="1"/>
-    <col min="6" max="6" width="72.4140625" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" customWidth="1"/>
+    <col min="5" max="5" width="55.28515625" customWidth="1"/>
+    <col min="6" max="6" width="72.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2114,6 +2431,12 @@
       <c r="F15" s="2" t="s">
         <v>78</v>
       </c>
+      <c r="G15" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="16" spans="2:8" ht="30" customHeight="1">
       <c r="B16" s="2" t="s">
@@ -2131,6 +2454,12 @@
       <c r="F16" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="G16" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="17" spans="2:9" ht="30" customHeight="1">
       <c r="B17" s="2" t="s">
@@ -2148,6 +2477,12 @@
       <c r="F17" s="2" t="s">
         <v>88</v>
       </c>
+      <c r="G17" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="18" spans="2:9" ht="45.75" customHeight="1">
       <c r="B18" s="2" t="s">
@@ -2165,7 +2500,12 @@
       <c r="F18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H18" s="7"/>
+      <c r="G18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>178</v>
+      </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="2:9" ht="27" customHeight="1">
@@ -2184,7 +2524,12 @@
       <c r="F19" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H19" s="7"/>
+      <c r="G19" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>179</v>
+      </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="2:9" ht="45" customHeight="1">
@@ -2203,7 +2548,12 @@
       <c r="F20" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="H20" s="7"/>
+      <c r="G20" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>180</v>
+      </c>
       <c r="I20" s="7"/>
     </row>
     <row r="21" spans="2:9" ht="27.75" customHeight="1">
@@ -2323,7 +2673,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="28">
+    <row r="26" spans="2:9" ht="30">
       <c r="B26" s="2" t="s">
         <v>129</v>
       </c>
@@ -2374,7 +2724,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="2:9">
+    <row r="29" spans="2:9" ht="30">
       <c r="B29" s="2" t="s">
         <v>144</v>
       </c>
@@ -2391,7 +2741,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="2:9" ht="28">
+    <row r="30" spans="2:9" ht="30">
       <c r="B30" s="2" t="s">
         <v>149</v>
       </c>
@@ -2408,7 +2758,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="28">
+    <row r="31" spans="2:9" ht="30">
       <c r="B31" s="2" t="s">
         <v>154</v>
       </c>
@@ -2425,7 +2775,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="28">
+    <row r="32" spans="2:9" ht="30">
       <c r="B32" s="2" t="s">
         <v>159</v>
       </c>
@@ -2461,15 +2811,21 @@
     <hyperlink ref="H23" location="'TC_21 Proof'!A1" display="TC_21 Proof" xr:uid="{CAAD97C3-3420-4F49-BCCA-D75D8B80AB8F}"/>
     <hyperlink ref="H24" location="'TC_22 Proof'!A1" display="TC_22 Proof" xr:uid="{C0E0F771-D2FB-46E8-B46B-518894807AAE}"/>
     <hyperlink ref="H25" location="'TC_23 Proof'!A1" display="TC_23 Proof" xr:uid="{24451747-D40D-4C32-8024-28412E7008EC}"/>
+    <hyperlink ref="H15" location="'TC_13 Proof'!A1" display="TC_13 Proof" xr:uid="{DF706E08-3958-426F-A80C-BCBB2B39FFE9}"/>
+    <hyperlink ref="H16" location="'TC_14 Proof'!A1" display="TC_14 Proof" xr:uid="{08CE8F99-6AE2-4E60-A2CC-83B74150FC7D}"/>
+    <hyperlink ref="H17" location="'TC_15 Proof'!A1" display="TC_15 Proof" xr:uid="{FE8465B1-B5B8-41E3-801C-E6778FAFAB20}"/>
+    <hyperlink ref="H18" location="'TC_16 Proof'!A1" display="TC_16 Proof" xr:uid="{F35C82B8-AC87-43CB-8464-BD59F03CF289}"/>
+    <hyperlink ref="H19" location="'TC_17 Proof'!A1" display="TC_17 Proof" xr:uid="{9DD67E73-9DB3-4D3E-A273-4DE660A666CE}"/>
+    <hyperlink ref="H20" location="'TC_18 Proof'!A1" display="TC_18 Proof" xr:uid="{CD93B397-7A46-4D98-A6F5-88C91E13C8EE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8222F65D-9425-4F3F-8617-B3720678BA88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2477,9 +2833,9 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14661779-2974-4C8F-A649-7A3252EF9A63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2487,9 +2843,9 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD94721-2605-46E8-9976-CD8971097348}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2497,9 +2853,9 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{637A21EA-F0D3-4556-9E93-B67F4B7E162B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2507,9 +2863,9 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B60C7F1-5496-4F79-A385-AA9E21CF3764}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2517,9 +2873,9 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5C26EE5-A387-4DEB-AF12-3C60E522327E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807BB318-320C-472B-B894-0C24E2BAB008}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2527,9 +2883,9 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A90DD207-1495-4605-80D8-A455910D4B21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8222F65D-9425-4F3F-8617-B3720678BA88}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2537,9 +2893,9 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FF9CC2B-650A-4A14-8506-33F382FBF334}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14661779-2974-4C8F-A649-7A3252EF9A63}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2547,89 +2903,149 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56E205E1-D54B-4272-8EC7-61B3ED6CECA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD94721-2605-46E8-9976-CD8971097348}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{637A21EA-F0D3-4556-9E93-B67F4B7E162B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C9D7DB-7990-4055-86EC-A375AFF7BC97}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B60C7F1-5496-4F79-A385-AA9E21CF3764}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5C26EE5-A387-4DEB-AF12-3C60E522327E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A90DD207-1495-4605-80D8-A455910D4B21}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FF9CC2B-650A-4A14-8506-33F382FBF334}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56E205E1-D54B-4272-8EC7-61B3ED6CECA9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{219B1214-897B-40C7-B3AF-A9BF8DC6F5F6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C44432-984D-4774-BEEE-1099B4C25EF4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAA4E696-1741-40E9-9CEA-570EB54840EC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49207123-E8E4-4B9C-879E-3D28500DF18F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36A15EEC-A60D-4F9C-ABD5-267CE5841ED1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807BB318-320C-472B-B894-0C24E2BAB008}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Extra/TestCase_CaroGame.xlsx
+++ b/Extra/TestCase_CaroGame.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Pictures\Network_Programming-UDM17_Group2\Extra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Network_Programming-UDM17_Group2\Extra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFCD827-E087-40F4-A5EE-1A108279E75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4ACDEC-149E-4EE1-8405-DAF6F175230B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="942" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="942" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="188">
   <si>
     <t>No</t>
   </si>
@@ -602,6 +602,27 @@
   </si>
   <si>
     <t>TC_18 Proof</t>
+  </si>
+  <si>
+    <t>TC_24 Proof</t>
+  </si>
+  <si>
+    <t>TC_25 Proof</t>
+  </si>
+  <si>
+    <t>TC_26 Proof</t>
+  </si>
+  <si>
+    <t>TC_27 Proof</t>
+  </si>
+  <si>
+    <t>TC_28 Proof</t>
+  </si>
+  <si>
+    <t>TC_29 Proof</t>
+  </si>
+  <si>
+    <t>TC_30 Proof</t>
   </si>
 </sst>
 </file>
@@ -686,7 +707,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -701,13 +722,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
-    <cellStyle name="Siêu kết nối" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2105,14 +2123,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:I32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="32.7109375" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" customWidth="1"/>
-    <col min="5" max="5" width="55.28515625" customWidth="1"/>
-    <col min="6" max="6" width="72.42578125" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" customWidth="1"/>
+    <col min="4" max="4" width="28.88671875" customWidth="1"/>
+    <col min="5" max="5" width="55.33203125" customWidth="1"/>
+    <col min="6" max="6" width="72.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2431,7 +2449,7 @@
       <c r="F15" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H15" s="9" t="s">
@@ -2454,7 +2472,7 @@
       <c r="F16" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H16" s="9" t="s">
@@ -2477,7 +2495,7 @@
       <c r="F17" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H17" s="9" t="s">
@@ -2500,7 +2518,7 @@
       <c r="F18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H18" s="9" t="s">
@@ -2524,7 +2542,7 @@
       <c r="F19" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="2" t="s">
         <v>168</v>
       </c>
       <c r="H19" s="9" t="s">
@@ -2548,7 +2566,7 @@
       <c r="F20" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="2" t="s">
         <v>168</v>
       </c>
       <c r="H20" s="9" t="s">
@@ -2673,7 +2691,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="30">
+    <row r="26" spans="2:9" ht="28.8">
       <c r="B26" s="2" t="s">
         <v>129</v>
       </c>
@@ -2688,6 +2706,12 @@
       </c>
       <c r="F26" s="2" t="s">
         <v>133</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="18.75" customHeight="1">
@@ -2706,6 +2730,12 @@
       <c r="F27" s="2" t="s">
         <v>138</v>
       </c>
+      <c r="G27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="28" spans="2:9" ht="28.5" customHeight="1">
       <c r="B28" s="2" t="s">
@@ -2723,8 +2753,14 @@
       <c r="F28" s="2" t="s">
         <v>143</v>
       </c>
+      <c r="G28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>183</v>
+      </c>
     </row>
-    <row r="29" spans="2:9" ht="30">
+    <row r="29" spans="2:9" ht="28.8">
       <c r="B29" s="2" t="s">
         <v>144</v>
       </c>
@@ -2740,8 +2776,14 @@
       <c r="F29" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="G29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>184</v>
+      </c>
     </row>
-    <row r="30" spans="2:9" ht="30">
+    <row r="30" spans="2:9" ht="28.8">
       <c r="B30" s="2" t="s">
         <v>149</v>
       </c>
@@ -2757,8 +2799,14 @@
       <c r="F30" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="G30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>185</v>
+      </c>
     </row>
-    <row r="31" spans="2:9" ht="30">
+    <row r="31" spans="2:9" ht="28.8">
       <c r="B31" s="2" t="s">
         <v>154</v>
       </c>
@@ -2774,8 +2822,14 @@
       <c r="F31" s="2" t="s">
         <v>158</v>
       </c>
+      <c r="G31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>186</v>
+      </c>
     </row>
-    <row r="32" spans="2:9" ht="30">
+    <row r="32" spans="2:9" ht="28.8">
       <c r="B32" s="2" t="s">
         <v>159</v>
       </c>
@@ -2790,6 +2844,12 @@
       </c>
       <c r="F32" s="2" t="s">
         <v>163</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2817,6 +2877,13 @@
     <hyperlink ref="H18" location="'TC_16 Proof'!A1" display="TC_16 Proof" xr:uid="{F35C82B8-AC87-43CB-8464-BD59F03CF289}"/>
     <hyperlink ref="H19" location="'TC_17 Proof'!A1" display="TC_17 Proof" xr:uid="{9DD67E73-9DB3-4D3E-A273-4DE660A666CE}"/>
     <hyperlink ref="H20" location="'TC_18 Proof'!A1" display="TC_18 Proof" xr:uid="{CD93B397-7A46-4D98-A6F5-88C91E13C8EE}"/>
+    <hyperlink ref="H26" r:id="rId1" xr:uid="{B725FD12-A2C1-4FC2-8832-4B0FBA99EE92}"/>
+    <hyperlink ref="H27" r:id="rId2" xr:uid="{5C913767-13AC-43B6-8883-C212D0EA4C2B}"/>
+    <hyperlink ref="H28" r:id="rId3" xr:uid="{DE4D5AAD-C77D-473D-8FFD-55D1DBACFF4E}"/>
+    <hyperlink ref="H29" r:id="rId4" xr:uid="{34F6F17C-E531-4181-B57A-CF24E45FFC4B}"/>
+    <hyperlink ref="H30" r:id="rId5" xr:uid="{F6931AB5-3B6E-4499-A5F5-15D94DFE5E49}"/>
+    <hyperlink ref="H31" r:id="rId6" xr:uid="{049C1879-A553-4586-B74C-6EEA1B6D55DC}"/>
+    <hyperlink ref="H32" r:id="rId7" xr:uid="{0B331F18-BC53-4D19-B943-04E9341C16BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2825,7 +2892,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2835,7 +2902,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2845,7 +2912,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2855,7 +2922,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2865,7 +2932,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2875,7 +2942,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807BB318-320C-472B-B894-0C24E2BAB008}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2885,7 +2952,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8222F65D-9425-4F3F-8617-B3720678BA88}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2895,7 +2962,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14661779-2974-4C8F-A649-7A3252EF9A63}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2905,7 +2972,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD94721-2605-46E8-9976-CD8971097348}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2915,7 +2982,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{637A21EA-F0D3-4556-9E93-B67F4B7E162B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2925,7 +2992,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C9D7DB-7990-4055-86EC-A375AFF7BC97}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2935,7 +3002,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B60C7F1-5496-4F79-A385-AA9E21CF3764}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2945,7 +3012,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5C26EE5-A387-4DEB-AF12-3C60E522327E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2955,7 +3022,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A90DD207-1495-4605-80D8-A455910D4B21}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2965,7 +3032,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FF9CC2B-650A-4A14-8506-33F382FBF334}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2975,7 +3042,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56E205E1-D54B-4272-8EC7-61B3ED6CECA9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2985,7 +3052,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{219B1214-897B-40C7-B3AF-A9BF8DC6F5F6}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2995,7 +3062,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C44432-984D-4774-BEEE-1099B4C25EF4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3005,7 +3072,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAA4E696-1741-40E9-9CEA-570EB54840EC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3015,7 +3082,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49207123-E8E4-4B9C-879E-3D28500DF18F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3025,7 +3092,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36A15EEC-A60D-4F9C-ABD5-267CE5841ED1}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3035,7 +3102,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3045,7 +3112,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
